--- a/output/Tables/Best practice/cases_prev_target.xlsx
+++ b/output/Tables/Best practice/cases_prev_target.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -428,22 +428,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>19602.90425826305</v>
+        <v>67831.23353178005</v>
       </c>
       <c r="C2">
-        <v>20228.64755061541</v>
+        <v>64140.09824029337</v>
       </c>
       <c r="D2">
-        <v>19245.09011269704</v>
+        <v>71676.42626977115</v>
       </c>
       <c r="E2">
-        <v>33731.29575366843</v>
+        <v>898015.3256691351</v>
       </c>
       <c r="F2">
-        <v>32447.03878180786</v>
+        <v>789521.0814270369</v>
       </c>
       <c r="G2">
-        <v>35164.55002382712</v>
+        <v>1000715.992652987</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,271 +455,228 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>4486262335.237902</v>
+        <v>119436038313.995</v>
       </c>
       <c r="L2">
-        <v>4315456157.980446</v>
+        <v>105006303829.7959</v>
       </c>
       <c r="M2">
-        <v>4676885153.169007</v>
+        <v>133095227022.8472</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B3">
-        <v>218.3914579478987</v>
+        <v>34747.93695221484</v>
       </c>
       <c r="C3">
-        <v>47.38016451848778</v>
+        <v>22934.66704436174</v>
       </c>
       <c r="D3">
-        <v>440.5675898233937</v>
+        <v>48046.76121846731</v>
       </c>
       <c r="E3">
-        <v>67.92137996698305</v>
+        <v>37063.73767520403</v>
       </c>
       <c r="F3">
-        <v>11.04893392343063</v>
+        <v>18145.15086012932</v>
       </c>
       <c r="G3">
-        <v>173.3705530459903</v>
+        <v>64005.82886381134</v>
       </c>
       <c r="H3">
-        <v>9628224.206548987</v>
+        <v>1935529584.112269</v>
       </c>
       <c r="I3">
-        <v>2088849.313126568</v>
+        <v>1277506823.705034</v>
       </c>
       <c r="J3">
-        <v>19423303.33254402</v>
+        <v>2676300693.391068</v>
       </c>
       <c r="K3">
-        <v>9033543.535608746</v>
+        <v>4929477110.802135</v>
       </c>
       <c r="L3">
-        <v>1469508.211816274</v>
+        <v>2413305064.3972</v>
       </c>
       <c r="M3">
-        <v>23058283.55511671</v>
+        <v>8512775238.886909</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B4">
-        <v>7988.423271897737</v>
+        <v>24703.20445271357</v>
       </c>
       <c r="C4">
-        <v>5887.00225096323</v>
+        <v>5138.496729763592</v>
       </c>
       <c r="D4">
-        <v>10442.35214437806</v>
+        <v>49902.7817067617</v>
       </c>
       <c r="E4">
-        <v>1264.207320064048</v>
+        <v>41336.84077089687</v>
       </c>
       <c r="F4">
-        <v>687.4914488283055</v>
+        <v>6640.150609691767</v>
       </c>
       <c r="G4">
-        <v>2082.093346576784</v>
+        <v>96496.53022861034</v>
       </c>
       <c r="H4">
-        <v>444971153.0912477</v>
+        <v>365780348.3313279</v>
       </c>
       <c r="I4">
-        <v>327917799.3831538</v>
+        <v>76085721.07760938</v>
       </c>
       <c r="J4">
-        <v>581659899.1461482</v>
+        <v>738910488.7320186</v>
       </c>
       <c r="K4">
-        <v>168139573.5685184</v>
+        <v>5497799822.529284</v>
       </c>
       <c r="L4">
-        <v>91436362.69416463</v>
+        <v>883140031.0890051</v>
       </c>
       <c r="M4">
-        <v>276918415.0947123</v>
+        <v>12834038520.40517</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B5">
-        <v>5491.999013354451</v>
+        <v>5883.080900132338</v>
       </c>
       <c r="C5">
-        <v>1189.692970718729</v>
+        <v>-452.3744842940446</v>
       </c>
       <c r="D5">
-        <v>11079.72937731247</v>
+        <v>11811.80000302952</v>
       </c>
       <c r="E5">
-        <v>1608.866972663388</v>
+        <v>12194.83219483917</v>
       </c>
       <c r="F5">
-        <v>274.9905066405875</v>
+        <v>-689.1592754673223</v>
       </c>
       <c r="G5">
-        <v>3748.265560937012</v>
+        <v>31038.7676911718</v>
       </c>
       <c r="H5">
-        <v>81320029.39073916</v>
+        <v>442413566.770853</v>
       </c>
       <c r="I5">
-        <v>17615783.81743215</v>
+        <v>-34019013.59339635</v>
       </c>
       <c r="J5">
-        <v>164057552.8898662</v>
+        <v>888259172.027818</v>
       </c>
       <c r="K5">
-        <v>213979307.3642306</v>
+        <v>1621912681.91361</v>
       </c>
       <c r="L5">
-        <v>36573737.38319813</v>
+        <v>-91658183.63715388</v>
       </c>
       <c r="M5">
-        <v>498519319.6046225</v>
+        <v>4128156102.92585</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B6">
-        <v>1160.599128691104</v>
+        <v>9343.926089853634</v>
       </c>
       <c r="C6">
-        <v>-91.71344517582934</v>
+        <v>7715.541055030125</v>
       </c>
       <c r="D6">
-        <v>2338.020564851662</v>
+        <v>10908.54917741606</v>
       </c>
       <c r="E6">
-        <v>418.9803065761039</v>
+        <v>17760.56967408254</v>
       </c>
       <c r="F6">
-        <v>-24.61038597440292</v>
+        <v>11072.52407616238</v>
       </c>
       <c r="G6">
-        <v>1071.442507600421</v>
+        <v>24490.5762785181</v>
       </c>
       <c r="H6">
-        <v>87278215.07669979</v>
+        <v>157342371.4270456</v>
       </c>
       <c r="I6">
-        <v>-6896942.790667498</v>
+        <v>129921995.8256526</v>
       </c>
       <c r="J6">
-        <v>175821484.4974105</v>
+        <v>183689059.5985096</v>
       </c>
       <c r="K6">
-        <v>55724380.77462182</v>
+        <v>2362155766.652978</v>
       </c>
       <c r="L6">
-        <v>-3273181.334595589</v>
+        <v>1472645702.129596</v>
       </c>
       <c r="M6">
-        <v>142501853.510856</v>
+        <v>3257246645.042908</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B7">
-        <v>2775.156531006049</v>
+        <v>136359.1833855172</v>
       </c>
       <c r="C7">
-        <v>2496.65359922797</v>
+        <v>97129.15216636291</v>
       </c>
       <c r="D7">
-        <v>3055.547676216799</v>
+        <v>168309.1713535821</v>
       </c>
       <c r="E7">
-        <v>629.3280609879164</v>
+        <v>414811.8425195308</v>
       </c>
       <c r="F7">
-        <v>427.5725263676822</v>
+        <v>182913.9621630865</v>
       </c>
       <c r="G7">
-        <v>822.8956375566999</v>
+        <v>782278.4877317447</v>
       </c>
       <c r="H7">
-        <v>46730860.82561098</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>42041149.9573998</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>51452367.31981476</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>83700632.11139289</v>
+        <v>55169975055.0976</v>
       </c>
       <c r="L7">
-        <v>56867146.00690173</v>
+        <v>24327556967.6905</v>
       </c>
       <c r="M7">
-        <v>109445119.7950411</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>31874.51014139424</v>
-      </c>
-      <c r="C8">
-        <v>22648.53551585891</v>
-      </c>
-      <c r="D8">
-        <v>39359.79779556325</v>
-      </c>
-      <c r="E8">
-        <v>33851.52549369234</v>
-      </c>
-      <c r="F8">
-        <v>14880.30972496569</v>
-      </c>
-      <c r="G8">
-        <v>63874.21852779593</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>4502252890.661081</v>
-      </c>
-      <c r="L8">
-        <v>1979081193.420437</v>
-      </c>
-      <c r="M8">
-        <v>8495271064.196858</v>
+        <v>104043038868.322</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Best practice/cases_prev_target.xlsx
+++ b/output/Tables/Best practice/cases_prev_target.xlsx
@@ -428,22 +428,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>67831.23353178005</v>
+        <v>154842.0388698892</v>
       </c>
       <c r="C2">
-        <v>64140.09824029337</v>
+        <v>118555.957455757</v>
       </c>
       <c r="D2">
-        <v>71676.42626977115</v>
+        <v>191419.1083091646</v>
       </c>
       <c r="E2">
-        <v>898015.3256691351</v>
+        <v>2149841.521652404</v>
       </c>
       <c r="F2">
-        <v>789521.0814270369</v>
+        <v>1525975.346744122</v>
       </c>
       <c r="G2">
-        <v>1000715.992652987</v>
+        <v>2765417.126847866</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,13 +455,13 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>119436038313.995</v>
+        <v>285928922379.7697</v>
       </c>
       <c r="L2">
-        <v>105006303829.7959</v>
+        <v>202954721116.9682</v>
       </c>
       <c r="M2">
-        <v>133095227022.8472</v>
+        <v>367800477870.7661</v>
       </c>
     </row>
     <row r="3">
@@ -471,40 +471,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>34747.93695221484</v>
+        <v>235592.0645089971</v>
       </c>
       <c r="C3">
-        <v>22934.66704436174</v>
+        <v>176874.2241128831</v>
       </c>
       <c r="D3">
-        <v>48046.76121846731</v>
+        <v>294428.2598532772</v>
       </c>
       <c r="E3">
-        <v>37063.73767520403</v>
+        <v>247711.4298645217</v>
       </c>
       <c r="F3">
-        <v>18145.15086012932</v>
+        <v>138732.6324744953</v>
       </c>
       <c r="G3">
-        <v>64005.82886381134</v>
+        <v>387435.8762907173</v>
       </c>
       <c r="H3">
-        <v>1935529584.112269</v>
+        <v>13122949177.28032</v>
       </c>
       <c r="I3">
-        <v>1277506823.705034</v>
+        <v>9852248031.535801</v>
       </c>
       <c r="J3">
-        <v>2676300693.391068</v>
+        <v>16400242930.34733</v>
       </c>
       <c r="K3">
-        <v>4929477110.802135</v>
+        <v>32945620171.98138</v>
       </c>
       <c r="L3">
-        <v>2413305064.3972</v>
+        <v>18451440119.10788</v>
       </c>
       <c r="M3">
-        <v>8512775238.886909</v>
+        <v>51528971546.6654</v>
       </c>
     </row>
     <row r="4">
@@ -514,40 +514,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>24703.20445271357</v>
+        <v>843249.6224298417</v>
       </c>
       <c r="C4">
-        <v>5138.496729763592</v>
+        <v>599477.0747796566</v>
       </c>
       <c r="D4">
-        <v>49902.7817067617</v>
+        <v>1083762.586691958</v>
       </c>
       <c r="E4">
-        <v>41336.84077089687</v>
+        <v>1379833.838623138</v>
       </c>
       <c r="F4">
-        <v>6640.150609691767</v>
+        <v>754007.1205024595</v>
       </c>
       <c r="G4">
-        <v>96496.53022861034</v>
+        <v>2076255.575124681</v>
       </c>
       <c r="H4">
-        <v>365780348.3313279</v>
+        <v>12485997159.31862</v>
       </c>
       <c r="I4">
-        <v>76085721.07760938</v>
+        <v>8876457046.262249</v>
       </c>
       <c r="J4">
-        <v>738910488.7320186</v>
+        <v>16047272621.1479</v>
       </c>
       <c r="K4">
-        <v>5497799822.529284</v>
+        <v>183517900536.8773</v>
       </c>
       <c r="L4">
-        <v>883140031.0890051</v>
+        <v>100282947026.8271</v>
       </c>
       <c r="M4">
-        <v>12834038520.40517</v>
+        <v>276141991491.5826</v>
       </c>
     </row>
     <row r="5">
@@ -557,40 +557,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>5883.080900132338</v>
+        <v>90132.19934243873</v>
       </c>
       <c r="C5">
-        <v>-452.3744842940446</v>
+        <v>63076.26199880906</v>
       </c>
       <c r="D5">
-        <v>11811.80000302952</v>
+        <v>116739.8264214146</v>
       </c>
       <c r="E5">
-        <v>12194.83219483917</v>
+        <v>184387.209398863</v>
       </c>
       <c r="F5">
-        <v>-689.1592754673223</v>
+        <v>94633.10615771161</v>
       </c>
       <c r="G5">
-        <v>31038.7676911718</v>
+        <v>305286.1355815424</v>
       </c>
       <c r="H5">
-        <v>442413566.770853</v>
+        <v>6778031522.75079</v>
       </c>
       <c r="I5">
-        <v>-34019013.59339635</v>
+        <v>4743397978.572485</v>
       </c>
       <c r="J5">
-        <v>888259172.027818</v>
+        <v>8778951686.716768</v>
       </c>
       <c r="K5">
-        <v>1621912681.91361</v>
+        <v>24523498850.04878</v>
       </c>
       <c r="L5">
-        <v>-91658183.63715388</v>
+        <v>12586203118.97564</v>
       </c>
       <c r="M5">
-        <v>4128156102.92585</v>
+        <v>40603056032.34515</v>
       </c>
     </row>
     <row r="6">
@@ -600,40 +600,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>9343.926089853634</v>
+        <v>42703.47928988576</v>
       </c>
       <c r="C6">
-        <v>7715.541055030125</v>
+        <v>33933.88718778748</v>
       </c>
       <c r="D6">
-        <v>10908.54917741606</v>
+        <v>51679.92168408018</v>
       </c>
       <c r="E6">
-        <v>17760.56967408254</v>
+        <v>79262.56133523512</v>
       </c>
       <c r="F6">
-        <v>11072.52407616238</v>
+        <v>47375.51274912129</v>
       </c>
       <c r="G6">
-        <v>24490.5762785181</v>
+        <v>113263.8574472768</v>
       </c>
       <c r="H6">
-        <v>157342371.4270456</v>
+        <v>719083887.7623776</v>
       </c>
       <c r="I6">
-        <v>129921995.8256526</v>
+        <v>571412726.3551449</v>
       </c>
       <c r="J6">
-        <v>183689059.5985096</v>
+        <v>870238201.2382264</v>
       </c>
       <c r="K6">
-        <v>2362155766.652978</v>
+        <v>10541920657.58627</v>
       </c>
       <c r="L6">
-        <v>1472645702.129596</v>
+        <v>6300943195.633132</v>
       </c>
       <c r="M6">
-        <v>3257246645.042908</v>
+        <v>15064093040.48781</v>
       </c>
     </row>
     <row r="7">
@@ -643,22 +643,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>136359.1833855172</v>
+        <v>1226552.033774374</v>
       </c>
       <c r="C7">
-        <v>97129.15216636291</v>
+        <v>859875.5612053685</v>
       </c>
       <c r="D7">
-        <v>168309.1713535821</v>
+        <v>1586998.450875154</v>
       </c>
       <c r="E7">
-        <v>414811.8425195308</v>
+        <v>3678587.473422583</v>
       </c>
       <c r="F7">
-        <v>182913.9621630865</v>
+        <v>1563126.141057551</v>
       </c>
       <c r="G7">
-        <v>782278.4877317447</v>
+        <v>7343286.10405276</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -670,13 +670,13 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>55169975055.0976</v>
+        <v>489252133965.2036</v>
       </c>
       <c r="L7">
-        <v>24327556967.6905</v>
+        <v>207895776760.6543</v>
       </c>
       <c r="M7">
-        <v>104043038868.322</v>
+        <v>976657051839.0171</v>
       </c>
     </row>
   </sheetData>
